--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-10-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">200mm Celotex XR4200 2.4m x 1.2m </t>
+          <t>200mm Celotex XR4200 2.4m x 1.2m  (Pallet of 12)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>£43.90</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.tradeinsulations.co.uk/product/celotex-cw4075-75mm-cavity-wall-board/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff649c1e8e5+80021]
-	GetHandleVerifier [0x0x7ff649c1e940+80112]
-	(No symbol) [0x0x7ff6499a060f]
-	(No symbol) [0x0x7ff6499f8854]
-	(No symbol) [0x0x7ff6499f8b1c]
-	(No symbol) [0x0x7ff649a4c927]
-	(No symbol) [0x0x7ff649a2126f]
-	(No symbol) [0x0x7ff649a4968a]
-	(No symbol) [0x0x7ff649a21003]
-	(No symbol) [0x0x7ff6499e95d1]
-	(No symbol) [0x0x7ff6499ea3f3]
-	GetHandleVerifier [0x0x7ff649eddc7d+2960429]
-	GetHandleVerifier [0x0x7ff649ed7f3a+2936554]
-	GetHandleVerifier [0x0x7ff649ef8977+3070247]
-	GetHandleVerifier [0x0x7ff649c383ce+185214]
-	GetHandleVerifier [0x0x7ff649c3fe1f+216527]
-	GetHandleVerifier [0x0x7ff649c27b24+117460]
-	GetHandleVerifier [0x0x7ff649c27cdf+117903]
-	GetHandleVerifier [0x0x7ff649c0dbb8+11112]
+	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
+	GetHandleVerifier [0x0x7ff758d5e940+80112]
+	(No symbol) [0x0x7ff758ae060f]
+	(No symbol) [0x0x7ff758b38854]
+	(No symbol) [0x0x7ff758b38b1c]
+	(No symbol) [0x0x7ff758b8c927]
+	(No symbol) [0x0x7ff758b6126f]
+	(No symbol) [0x0x7ff758b8968a]
+	(No symbol) [0x0x7ff758b61003]
+	(No symbol) [0x0x7ff758b295d1]
+	(No symbol) [0x0x7ff758b2a3f3]
+	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
+	GetHandleVerifier [0x0x7ff759017f3a+2936554]
+	GetHandleVerifier [0x0x7ff759038977+3070247]
+	GetHandleVerifier [0x0x7ff758d783ce+185214]
+	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
+	GetHandleVerifier [0x0x7ff758d67b24+117460]
+	GetHandleVerifier [0x0x7ff758d67cdf+117903]
+	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-10-2025.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£9.99</t>
+          <t>£9.89</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£9.99</t>
+          <t>£9.98</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£9.94</t>
+          <t>£9.85</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>£11.29</t>
+          <t>£11.20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>£11.21</t>
+          <t>£11.15</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -805,7 +805,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£14.59</t>
+          <t>£14.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.44</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -926,7 +926,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£14.90</t>
+          <t>£14.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>£14.80</t>
+          <t>£14.69</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£18.98</t>
+          <t>£18.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>£18.82</t>
+          <t>£18.73</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£20.69</t>
+          <t>£20.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£20.68</t>
+          <t>£20.62</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>£20.53</t>
+          <t>£20.43</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£20.90</t>
+          <t>£20.69</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£20.73</t>
+          <t>£20.63</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£23.98</t>
+          <t>£23.74</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>£23.79</t>
+          <t>£23.67</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1531,14 +1531,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>£25.74</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>£25.98</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>£25.98</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>£29.33</t>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>£25.78</t>
+          <t>£25.65</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£25.70</t>
+          <t>£25.24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£25.45</t>
+          <t>£25.32</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>£32.99</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£31.39</t>
+          <t>£31.27</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>£31.11</t>
+          <t>£30.95</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£39.69</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£38.53</t>
+          <t>£38.34</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£39.48</t>
+          <t>£37.99</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£38.64</t>
+          <t>£38.59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>£38.32</t>
+          <t>£38.13</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£38.29</t>
+          <t>£37.99</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£38.28</t>
+          <t>£37.84</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£37.94</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>£695.52</t>
+          <t>£692.04</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>£873.16</t>
+          <t>£868.79</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>£28.94</t>
+          <t>£28.14</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>£28.27</t>
+          <t>£28.13</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>£34.59</t>
+          <t>£34.04</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>£34.13</t>
+          <t>£33.96</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>£39.09</t>
+          <t>£36.99</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>£37.05</t>
+          <t>£36.86</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>£42.19</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>£42.24</t>
+          <t>£42.03</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://www.tradeinsulations.co.uk/product/celotex-cw4075-75mm-cavity-wall-board/</t>
+          <t>£43.90</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>£1787.2</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff758d5e8e5+80021]
-	GetHandleVerifier [0x0x7ff758d5e940+80112]
-	(No symbol) [0x0x7ff758ae060f]
-	(No symbol) [0x0x7ff758b38854]
-	(No symbol) [0x0x7ff758b38b1c]
-	(No symbol) [0x0x7ff758b8c927]
-	(No symbol) [0x0x7ff758b6126f]
-	(No symbol) [0x0x7ff758b8968a]
-	(No symbol) [0x0x7ff758b61003]
-	(No symbol) [0x0x7ff758b295d1]
-	(No symbol) [0x0x7ff758b2a3f3]
-	GetHandleVerifier [0x0x7ff75901dc7d+2960429]
-	GetHandleVerifier [0x0x7ff759017f3a+2936554]
-	GetHandleVerifier [0x0x7ff759038977+3070247]
-	GetHandleVerifier [0x0x7ff758d783ce+185214]
-	GetHandleVerifier [0x0x7ff758d7fe1f+216527]
-	GetHandleVerifier [0x0x7ff758d67b24+117460]
-	GetHandleVerifier [0x0x7ff758d67cdf+117903]
-	GetHandleVerifier [0x0x7ff758d4dbb8+11112]
+	GetHandleVerifier [0x0x7ff74d07e8e5+80021]
+	GetHandleVerifier [0x0x7ff74d07e940+80112]
+	(No symbol) [0x0x7ff74ce0060f]
+	(No symbol) [0x0x7ff74ce58854]
+	(No symbol) [0x0x7ff74ce58b1c]
+	(No symbol) [0x0x7ff74ceac927]
+	(No symbol) [0x0x7ff74ce8126f]
+	(No symbol) [0x0x7ff74cea968a]
+	(No symbol) [0x0x7ff74ce81003]
+	(No symbol) [0x0x7ff74ce495d1]
+	(No symbol) [0x0x7ff74ce4a3f3]
+	GetHandleVerifier [0x0x7ff74d33dc7d+2960429]
+	GetHandleVerifier [0x0x7ff74d337f3a+2936554]
+	GetHandleVerifier [0x0x7ff74d358977+3070247]
+	GetHandleVerifier [0x0x7ff74d0983ce+185214]
+	GetHandleVerifier [0x0x7ff74d09fe1f+216527]
+	GetHandleVerifier [0x0x7ff74d087b24+117460]
+	GetHandleVerifier [0x0x7ff74d087cdf+117903]
+	GetHandleVerifier [0x0x7ff74d06dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>£1123.52</t>
+          <t>£1117.92</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>£1248.32</t>
+          <t>£1242.08</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>£1183.2</t>
+          <t>£1177.28</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
